--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104523_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104523_W8.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1792</v>
+        <v>1.1748</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8249</v>
+        <v>-0.2243</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6457000000000001</v>
+        <v>1.3991</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1484</v>
+        <v>-0.5977</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2004</v>
+        <v>-0.4025</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3488</v>
+        <v>-0.1952</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2492</v>
+        <v>-0.972</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0999</v>
+        <v>-0.1002</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>-0.8718</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8992</v>
+        <v>0.3743</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3003</v>
+        <v>-0.3023</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1995</v>
+        <v>0.6766</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1747</v>
+        <v>-0.3657</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8026</v>
+        <v>-0.272</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6279</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V2" t="n">
-        <v>-2.7317</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7317</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>L. COSTA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9091</v>
+        <v>1.0319</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2673</v>
+        <v>5.1546</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.3582</v>
+        <v>-4.1227</v>
       </c>
       <c r="G3" t="n">
-        <v>0.403</v>
+        <v>3.257</v>
       </c>
       <c r="H3" t="n">
-        <v>2.0289</v>
+        <v>-1.3361</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6259</v>
+        <v>4.5931</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6899</v>
+        <v>8.477600000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3913</v>
+        <v>1.5373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2985</v>
+        <v>6.9403</v>
       </c>
       <c r="M3" t="n">
-        <v>-4.2869</v>
+        <v>-5.2207</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3624</v>
+        <v>-2.8734</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9245</v>
+        <v>-2.3472</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7064</v>
+        <v>-0.3357</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5243</v>
+        <v>-0.4533</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1821</v>
+        <v>0.1176</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.387</v>
       </c>
       <c r="W3" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>J. KLJAJIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6840000000000001</v>
+        <v>1.0011</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0566</v>
+        <v>3.1813</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3727</v>
+        <v>-2.1803</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.7058</v>
+        <v>0.6395</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6001</v>
+        <v>-1.0375</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1057</v>
+        <v>1.677</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2721</v>
+        <v>1.7704</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5204</v>
+        <v>-0.0312</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7517</v>
+        <v>1.8016</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.4337</v>
+        <v>-1.1309</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.0797</v>
+        <v>-1.0062</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.354</v>
+        <v>-0.1246</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8169</v>
+        <v>-0.3017</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2511</v>
+        <v>-0.2232</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5658</v>
+        <v>-0.0785</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4387</v>
+        <v>-0.7025</v>
       </c>
       <c r="W4" t="n">
-        <v>3.4387</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6486</v>
+        <v>0.1614</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6264</v>
+        <v>0.8355</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2751</v>
+        <v>-0.6741</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6045</v>
+        <v>-4.7107</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4099</v>
+        <v>-2.6074</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1946</v>
+        <v>-2.1032</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9574</v>
+        <v>-1.3126</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.5526</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8637</v>
+        <v>-0.7601</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3529</v>
+        <v>-3.398</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3162</v>
+        <v>-2.0549</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6691</v>
+        <v>-1.3432</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.881</v>
+        <v>0.3077</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>0.0877</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1854</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5463</v>
+        <v>3.4262</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>3.4262</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. KLJAJIC</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5737</v>
+        <v>0.0815</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6698</v>
+        <v>0.5084</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0961</v>
+        <v>-0.4269</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6353</v>
+        <v>1.1467</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0492</v>
+        <v>-0.2092</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6846</v>
+        <v>1.3559</v>
       </c>
       <c r="J6" t="n">
-        <v>1.796</v>
+        <v>0.2277</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0244</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8204</v>
+        <v>0.1489</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1606</v>
+        <v>0.919</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0248</v>
+        <v>-0.2879</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1359</v>
+        <v>1.2069</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.8211</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.06510000000000001</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.4433</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-2.7237</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-0.7156</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.7652</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.0496</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.7071</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.639</v>
-      </c>
       <c r="X6" t="n">
-        <v>-2.3461</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. COSTA</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3591</v>
+        <v>-0.4579</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5524</v>
+        <v>2.9309</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.1933</v>
+        <v>-3.3888</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2674</v>
+        <v>0.4018</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3464</v>
+        <v>2.0223</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6139</v>
+        <v>-1.6205</v>
       </c>
       <c r="J7" t="n">
-        <v>8.5215</v>
+        <v>4.6621</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5514</v>
+        <v>4.3642</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9701</v>
+        <v>0.2979</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.2541</v>
+        <v>-4.2602</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.8978</v>
+        <v>-2.3419</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3563</v>
+        <v>-1.9184</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0256</v>
+        <v>0.3483</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.113</v>
+        <v>0.2296</v>
       </c>
       <c r="U7" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.1187</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7373</v>
+        <v>-0.4864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1524</v>
+        <v>0.3247</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8897</v>
+        <v>-0.8111</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9231</v>
+        <v>-0.9198</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9524</v>
+        <v>-0.948</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0293</v>
+        <v>0.0283</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3395</v>
+        <v>0.3273</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1803</v>
+        <v>-0.1864</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2626</v>
+        <v>-1.2471</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5873</v>
+        <v>-0.339</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3478</v>
+        <v>-0.1604</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2395</v>
+        <v>-0.1786</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1679</v>
+        <v>-1.978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0075</v>
+        <v>0.1252</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1754</v>
+        <v>-2.1033</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2743</v>
+        <v>-0.2695</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3276</v>
+        <v>-0.3247</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0533</v>
+        <v>0.0552</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1466</v>
+        <v>0.1462</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L9" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4209</v>
+        <v>-0.4157</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3622</v>
+        <v>-0.3592</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2547</v>
+        <v>-0.0743</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5519</v>
+        <v>-2.6072</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0685</v>
+        <v>-0.2916</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4834</v>
+        <v>-2.3156</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2706</v>
+        <v>0.2741</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4245</v>
+        <v>-1.4055</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6951</v>
+        <v>1.6796</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0067</v>
+        <v>1.9814</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4502</v>
+        <v>0.4482</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5565</v>
+        <v>1.5333</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7361</v>
+        <v>-1.7073</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8747</v>
+        <v>-1.8536</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.713</v>
+        <v>-0.7643</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0434</v>
+        <v>-0.2164</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6696</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0404</v>
+        <v>-4.7044</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3858</v>
+        <v>-0.0549</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.6546</v>
+        <v>-4.6495</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8258</v>
+        <v>-1.8274</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.645</v>
+        <v>-0.6462</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1808</v>
+        <v>-1.1813</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6758</v>
+        <v>0.6538</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6785</v>
+        <v>0.6615</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5016</v>
+        <v>-2.4813</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3234</v>
+        <v>-1.3077</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1369</v>
+        <v>-0.8166</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.4387</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.143799999999999</v>
+        <v>-6.783199999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>12.4502</v>
+        <v>12.4898</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.594</v>
+        <v>-19.2732</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6088</v>
+        <v>-2.606</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.926600000000001</v>
+        <v>-6.894800000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.318000000000001</v>
+        <v>4.2889</v>
       </c>
       <c r="J12" t="n">
-        <v>16.1957</v>
+        <v>15.9619</v>
       </c>
       <c r="K12" t="n">
-        <v>6.387099999999999</v>
+        <v>6.254</v>
       </c>
       <c r="L12" t="n">
-        <v>9.808399999999999</v>
+        <v>9.707699999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-18.8044</v>
+        <v>-18.5679</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.3136</v>
+        <v>-13.1488</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.4905</v>
+        <v>-5.4191</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1341</v>
+        <v>1.1382</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.4757</v>
+        <v>-12.5197</v>
       </c>
       <c r="R12" t="n">
-        <v>13.61</v>
+        <v>13.6579</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6161</v>
+        <v>-2.2762</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3608</v>
+        <v>-1.0017</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2551</v>
+        <v>-1.2746</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.0533</v>
+        <v>-3.0392</v>
       </c>
       <c r="W12" t="n">
-        <v>10.0912</v>
+        <v>10.0493</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.1445</v>
+        <v>-13.0886</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0102</v>
+        <v>4.3851</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6033</v>
+        <v>5.1266</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.593</v>
+        <v>-0.7415</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8816</v>
+        <v>3.8638</v>
       </c>
       <c r="H13" t="n">
-        <v>3.058</v>
+        <v>3.0369</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8237</v>
+        <v>0.8269</v>
       </c>
       <c r="J13" t="n">
-        <v>5.9727</v>
+        <v>5.925</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7364</v>
+        <v>3.6984</v>
       </c>
       <c r="L13" t="n">
-        <v>2.2363</v>
+        <v>2.2265</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0911</v>
+        <v>-2.0612</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6785</v>
+        <v>-0.6615</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.4126</v>
+        <v>-1.3997</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2855</v>
+        <v>0.1163</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5492</v>
+        <v>0.3605</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9604</v>
+        <v>1.9497</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1985</v>
+        <v>3.4385</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9143</v>
+        <v>3.4822</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2842</v>
+        <v>-0.0437</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6229</v>
+        <v>1.8801</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8095</v>
+        <v>3.1744</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1866</v>
+        <v>-1.2943</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4909</v>
+        <v>3.8254</v>
       </c>
       <c r="K14" t="n">
-        <v>1.638</v>
+        <v>3.5056</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8529</v>
+        <v>0.3198</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.868</v>
+        <v>-1.9453</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1715</v>
+        <v>-0.3312</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0395</v>
+        <v>-1.6141</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4537</v>
+        <v>-2.5039</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4681</v>
+        <v>0.2916</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8771</v>
+        <v>0.2111</v>
       </c>
       <c r="U14" t="n">
-        <v>0.591</v>
+        <v>0.0805</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2534</v>
+        <v>1.9497</v>
       </c>
       <c r="W14" t="n">
+        <v>1.9497</v>
+      </c>
+      <c r="X14" t="n">
         <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-1.2534</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1862</v>
+        <v>2.7333</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4222</v>
+        <v>3.1635</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.236</v>
+        <v>-0.4302</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8896</v>
+        <v>1.7821</v>
       </c>
       <c r="H15" t="n">
-        <v>3.1877</v>
+        <v>0.1463</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2981</v>
+        <v>1.6358</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8662</v>
+        <v>2.8131</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5357</v>
+        <v>0.9513</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3304</v>
+        <v>1.8618</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9765</v>
+        <v>-1.031</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.348</v>
+        <v>-0.805</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6285</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-0.6829</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0166</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0907</v>
+        <v>-0.214</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0741</v>
+        <v>0.2058</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9604</v>
+        <v>0.0488</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9604</v>
+        <v>1.2472</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.804</v>
+        <v>2.5459</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4225</v>
+        <v>2.5558</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6185</v>
+        <v>-0.0098</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7741</v>
+        <v>-1.2139</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1428</v>
+        <v>0.8302</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6313</v>
+        <v>-2.0441</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8285</v>
+        <v>-0.5289</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9626</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8658</v>
+        <v>-1.4457</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0543</v>
+        <v>-0.6851</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8198</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2345</v>
+        <v>-0.5984</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.6805</v>
+        <v>-0.4553</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0711</v>
+        <v>0.1451</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0212</v>
+        <v>0.2715</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0499</v>
+        <v>-0.1264</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0515</v>
+        <v>3.1595</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>3.2684</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2019</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1152</v>
+        <v>2.1415</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2388</v>
+        <v>1.944</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1237</v>
+        <v>0.1974</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2039</v>
+        <v>1.6232</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8326</v>
+        <v>1.8094</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.0365</v>
+        <v>-0.1862</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5009</v>
+        <v>2.4646</v>
       </c>
       <c r="K17" t="n">
-        <v>0.928</v>
+        <v>1.6235</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4289</v>
+        <v>0.8411</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.703</v>
+        <v>-0.8414</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0954</v>
+        <v>0.1859</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6077</v>
+        <v>-1.0273</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3033</v>
+        <v>0.3997</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0847</v>
+        <v>-0.0653</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2187</v>
+        <v>0.465</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1687</v>
+        <v>-1.2472</v>
       </c>
       <c r="W17" t="n">
-        <v>3.278</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1093</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0874</v>
+        <v>1.9136</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1042</v>
+        <v>2.9589</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0169</v>
+        <v>-1.0453</v>
       </c>
       <c r="G18" t="n">
-        <v>3.3443</v>
+        <v>3.3499</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4588</v>
+        <v>3.4553</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1145</v>
+        <v>-0.1054</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1377</v>
+        <v>4.1204</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4287</v>
+        <v>3.4129</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8111</v>
+        <v>0.632</v>
       </c>
       <c r="T18" t="n">
-        <v>0.369</v>
+        <v>0.253</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4422</v>
+        <v>0.379</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2077</v>
+        <v>0.1126</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5058</v>
+        <v>1.1846</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7135</v>
+        <v>-1.072</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6379</v>
+        <v>0.2821</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7605</v>
+        <v>0.7379</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1227</v>
+        <v>-0.4558</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5261</v>
+        <v>1.3844</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1456</v>
+        <v>0.9825</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6717</v>
+        <v>0.4019</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1639</v>
+        <v>-1.1023</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6149</v>
+        <v>-0.2446</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>-0.8578</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8147</v>
+        <v>-0.2276</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1272</v>
+        <v>-0.0801</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7017</v>
+        <v>0.0278</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4255</v>
+        <v>-0.1078</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4371</v>
+        <v>-0.5447</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6556</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3485</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9593</v>
+        <v>1.1826</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3078</v>
+        <v>-1.7577</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2786</v>
+        <v>-2.3306</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7344000000000001</v>
+        <v>-1.528</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4558</v>
+        <v>-0.8026</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3948</v>
+        <v>-0.8126</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9871</v>
+        <v>-0.9243</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4078</v>
+        <v>0.1117</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1162</v>
+        <v>-1.518</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2526</v>
+        <v>-0.6037</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8636</v>
+        <v>-0.9143</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5344</v>
+        <v>0.18</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>0.2715</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3257</v>
+        <v>-0.0915</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5463</v>
+        <v>0.665</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5463</v>
+        <v>-1.5139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8443000000000001</v>
+        <v>0.1373</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6955</v>
+        <v>-0.9106</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3398</v>
+        <v>-0.6273</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5296</v>
+        <v>-0.7556</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8103</v>
+        <v>0.1284</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8027</v>
+        <v>0.5184</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9147</v>
+        <v>-0.1519</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.6703</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5371</v>
+        <v>-1.1457</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9222</v>
+        <v>-0.5419</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4537</v>
+        <v>-1.8211</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0808</v>
+        <v>0.5563</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0847</v>
+        <v>0.3505</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0039</v>
+        <v>0.2058</v>
       </c>
       <c r="V21" t="n">
-        <v>0.662</v>
+        <v>0.4358</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5234</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9957</v>
+        <v>-1.1216</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3515</v>
+        <v>-0.3571</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6442</v>
+        <v>-0.7645</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2998</v>
+        <v>-0.2979</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1212</v>
+        <v>-0.1207</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6088</v>
+        <v>0.6061</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5715</v>
+        <v>0.5688</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9086</v>
+        <v>-0.9039</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0835</v>
+        <v>-0.2091</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2643</v>
+        <v>0.1394</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2544</v>
+        <v>-2.068</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8522</v>
+        <v>-0.7371</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4022</v>
+        <v>-1.3309</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3506</v>
+        <v>-2.3465</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.5829</v>
+        <v>-1.5825</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6798</v>
+        <v>-0.6835</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7171</v>
+        <v>-0.7207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6708</v>
+        <v>-1.6631</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.2786</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0544</v>
+        <v>0.174</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6</v>
+        <v>-5.6007</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.217</v>
+        <v>-1.3682</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.383</v>
+        <v>-4.2324</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3504</v>
+        <v>-3.3591</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3029</v>
+        <v>-2.3088</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0476</v>
+        <v>-1.0503</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0379</v>
+        <v>-1.0647</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.3125</v>
+        <v>-2.2945</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6062</v>
+        <v>-1.5946</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3133</v>
+        <v>0.3227</v>
       </c>
       <c r="T24" t="n">
-        <v>0.7017</v>
+        <v>0.5874</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3883</v>
+        <v>-0.2647</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W24" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.909</v>
+        <v>-1.9009</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.143900000000002</v>
+        <v>7.1318</v>
       </c>
       <c r="E25" t="n">
-        <v>19.594</v>
+        <v>19.2731</v>
       </c>
       <c r="F25" t="n">
-        <v>-12.4501</v>
+        <v>-12.1412</v>
       </c>
       <c r="G25" t="n">
-        <v>2.608700000000001</v>
+        <v>2.605899999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>6.926699999999999</v>
+        <v>6.8948</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.3179</v>
+        <v>-4.2888</v>
       </c>
       <c r="J25" t="n">
-        <v>18.8044</v>
+        <v>18.56770000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>13.3139</v>
+        <v>13.1487</v>
       </c>
       <c r="L25" t="n">
-        <v>5.4903</v>
+        <v>5.4188</v>
       </c>
       <c r="M25" t="n">
-        <v>-16.1955</v>
+        <v>-15.9619</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.3872</v>
+        <v>-6.2539</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.808400000000001</v>
+        <v>-9.707799999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6101</v>
+        <v>-13.6578</v>
       </c>
       <c r="R25" t="n">
-        <v>12.4758</v>
+        <v>12.5198</v>
       </c>
       <c r="S25" t="n">
-        <v>2.6161</v>
+        <v>2.6249</v>
       </c>
       <c r="T25" t="n">
-        <v>1.2552</v>
+        <v>1.2748</v>
       </c>
       <c r="U25" t="n">
-        <v>1.3609</v>
+        <v>1.3502</v>
       </c>
       <c r="V25" t="n">
-        <v>3.053199999999999</v>
+        <v>3.0393</v>
       </c>
       <c r="W25" t="n">
-        <v>13.1444</v>
+        <v>13.0884</v>
       </c>
       <c r="X25" t="n">
-        <v>-10.0913</v>
+        <v>-10.0492</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104523_W8.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104523_W8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-13.0886</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.5139</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.9009</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104523_W8.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-10.0492</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
